--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_gard_task.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_gard_task.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_gardTask" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcMode="manual"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="57">
   <si>
     <t>唯一id</t>
   </si>
@@ -154,10 +154,10 @@
     <t>全员消灭5只野外BOSS</t>
   </si>
   <si>
-    <t>10010002#125000</t>
-  </si>
-  <si>
-    <t>10090001#4000</t>
+    <t>10010002#50000</t>
+  </si>
+  <si>
+    <t>10090001#2000</t>
   </si>
   <si>
     <t>2</t>
@@ -166,21 +166,21 @@
     <t>40006#50012#60008#70007#80006#80007#11010#90008#14012#5</t>
   </si>
   <si>
+    <t>openUIPanel#dev/outui/ChallengeBoss/Panel/KLChallengeBoss/KLChallengeBossPanel#1#monsterType=2</t>
+  </si>
+  <si>
+    <t>全员通关40次恶魔广场</t>
+  </si>
+  <si>
+    <t>10001#40</t>
+  </si>
+  <si>
+    <t>transferNPC#100406</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
-    <t>openUIPanel#dev/outui/ChallengeBoss/Panel/KLChallengeBoss/KLChallengeBossPanel#1#monsterType=2</t>
-  </si>
-  <si>
-    <t>全员通关40次恶魔广场</t>
-  </si>
-  <si>
-    <t>10001#40</t>
-  </si>
-  <si>
-    <t>transferNPC#100406</t>
-  </si>
-  <si>
     <t>全员通关40次血色城堡</t>
   </si>
   <si>
@@ -196,13 +196,28 @@
     <t>全员消灭100名敌方玩家</t>
   </si>
   <si>
-    <t>10090001#3000</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
     <t>openUIPanel#dev/ui/Map/Panel/KLBigMap/KLBigMapPanel</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>全员参加狼魂要塞50次</t>
+  </si>
+  <si>
+    <t>15001#50</t>
+  </si>
+  <si>
+    <t>全员参加罗兰攻城战50次</t>
+  </si>
+  <si>
+    <t>16001#50</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
 </sst>
 </file>
@@ -861,7 +876,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -880,8 +895,17 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -890,19 +914,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1267,11 +1279,11 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="113" customHeight="1" spans="3:10">
+    <row r="2" s="1" customFormat="1" ht="113" customHeight="1" spans="1:10">
       <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
@@ -1293,7 +1305,7 @@
       <c r="I2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1304,10 +1316,10 @@
       <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -1325,7 +1337,7 @@
       <c r="I3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="7" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1336,10 +1348,10 @@
       <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -1357,167 +1369,222 @@
       <c r="I4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:10">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="7" t="s">
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="12">
+        <v>3</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="7">
+      <c r="H6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="12">
         <v>3</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="F7" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D8" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="9">
-        <v>3</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="9">
-        <v>3</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="E8" s="12">
+        <v>4</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:10">
+      <c r="A9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D9" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="9">
-        <v>3</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="9">
-        <v>3</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="E9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:10">
+      <c r="A10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="9">
-        <v>4</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="9">
-        <v>3</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="D10" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="5:5">
-      <c r="E10" s="13"/>
-    </row>
-    <row r="11" customHeight="1" spans="5:5">
-      <c r="E11" s="13"/>
-    </row>
-    <row r="12" customHeight="1" spans="5:5">
-      <c r="E12" s="13"/>
-    </row>
-    <row r="13" customHeight="1" spans="5:5">
-      <c r="E13" s="13"/>
-    </row>
-    <row r="14" customHeight="1" spans="5:5">
-      <c r="E14" s="13"/>
-    </row>
-    <row r="15" customHeight="1" spans="5:5">
-      <c r="E15" s="13"/>
-    </row>
-    <row r="16" customHeight="1" spans="5:5">
-      <c r="E16" s="13"/>
+      <c r="F10" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:10">
+      <c r="E11" s="15"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:10">
+      <c r="E12" s="15"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:10">
+      <c r="E13" s="15"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:10">
+      <c r="E14" s="15"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:10">
+      <c r="E15" s="15"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:10">
+      <c r="E16" s="15"/>
     </row>
     <row r="17" customHeight="1" spans="5:5">
-      <c r="E17" s="13"/>
+      <c r="E17" s="15"/>
     </row>
     <row r="18" customHeight="1" spans="5:5">
-      <c r="E18" s="13"/>
+      <c r="E18" s="15"/>
     </row>
     <row r="19" customHeight="1" spans="5:5">
-      <c r="E19" s="13"/>
+      <c r="E19" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
